--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111514343</v>
+        <v>119002685</v>
       </c>
       <c r="B2" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +710,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mumsarby 1107 m NW, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655377.8501467675</v>
+        <v>655276</v>
       </c>
       <c r="R2" t="n">
-        <v>6675763.565543589</v>
+        <v>6675628</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,56 +786,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111685514</v>
+        <v>111514314</v>
       </c>
       <c r="B3" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mumsarby , Upl</t>
+          <t>Mumsarby 1049 m NW, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655384</v>
+        <v>655238</v>
       </c>
       <c r="R3" t="n">
-        <v>6675716</v>
+        <v>6675618</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,27 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lång rad med fruktkroppar nära ett kärr där en del gran finns, annars mest tall runtomkring.</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,62 +904,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111685525</v>
+        <v>112071514</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>720</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mumsarby , Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655286</v>
+        <v>655235</v>
       </c>
       <c r="R4" t="n">
-        <v>6675700</v>
+        <v>6675613</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,22 +972,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Samma plats som tidigare.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,15 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119002668</v>
+        <v>119002667</v>
       </c>
       <c r="B5" t="n">
-        <v>80468</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655283</v>
+        <v>655346</v>
       </c>
       <c r="R5" t="n">
-        <v>6675703</v>
+        <v>6675637</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,49 +1129,36 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119002680</v>
+        <v>119002668</v>
       </c>
       <c r="B6" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1202,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655280</v>
+        <v>655283</v>
       </c>
       <c r="R6" t="n">
-        <v>6675629</v>
+        <v>6675703</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1237,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,37 +1239,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119002682</v>
+        <v>107121708</v>
       </c>
       <c r="B7" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>1106</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1321,17 +1281,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Persbomossen, Upl</t>
+          <t>Mumsarby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655276</v>
+        <v>655391</v>
       </c>
       <c r="R7" t="n">
-        <v>6675638</v>
+        <v>6675668</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,22 +1315,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2023-03-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,8 +1329,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,41 +1363,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119002667</v>
+        <v>119002680</v>
       </c>
       <c r="B8" t="n">
-        <v>80468</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1440,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655346</v>
+        <v>655280</v>
       </c>
       <c r="R8" t="n">
-        <v>6675637</v>
+        <v>6675629</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1475,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,15 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119002698</v>
+        <v>119002682</v>
       </c>
       <c r="B9" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,27 +1492,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1556,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655287</v>
+        <v>655276</v>
       </c>
       <c r="R9" t="n">
-        <v>6675660</v>
+        <v>6675638</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1591,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,42 +1599,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119002672</v>
+        <v>112071516</v>
       </c>
       <c r="B10" t="n">
-        <v>90075</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5754</v>
+        <v>5747</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655294</v>
+        <v>655233</v>
       </c>
       <c r="R10" t="n">
-        <v>6675660</v>
+        <v>6675613</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1709,30 +1675,36 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rätt fuktig mark med gran och tall. Ca 10x15 cm bred och drygt 15 cm hög ovan mark. Klen, torr, vitaktig fot. Ljusgula, långa grenar med klargula toppar. Doftar svagt, lite smörigt. Kan ej beskriva smaken. Efter ett dygn i plastpåse doftar den svagt av läder/saffran om grenarna, samma doft som vedticka men mycket svagare.</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1751,15 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119002685</v>
+        <v>119002672</v>
       </c>
       <c r="B11" t="n">
-        <v>95453</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,27 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>5754</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1795,10 +1769,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655276</v>
+        <v>655294</v>
       </c>
       <c r="R11" t="n">
-        <v>6675628</v>
+        <v>6675660</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1830,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1864,6 +1838,1038 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111685514</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mumsarby , Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>655384</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6675716</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lång rad med fruktkroppar nära ett kärr där en del gran finns, annars mest tall runtomkring.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111685525</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mumsarby , Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>655287</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6675700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111474623</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mumsarby 1089 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>655407</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6675770</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111514338</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mumsarby 1046 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>655238</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6675614</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>111514339</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mumsarby 1093 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>655411</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6675762</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111514343</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mumsarby 1107 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>655378</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6675763</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>119002698</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>655287</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6675660</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>119002700</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Valtins, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>655395</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6675760</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112071519</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>655241</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6675610</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fuktig mark med gran och tall. Ca 15 cm hög. Vitaktiga/cremefärgade grenar. Liten bit insamlad.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119002680</v>
+        <v>135229477</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,34 +1374,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1409,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655280</v>
+        <v>655340</v>
       </c>
       <c r="R8" t="n">
-        <v>6675629</v>
+        <v>6675648</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1439,22 +1432,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,7 +1474,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119002682</v>
+        <v>119002680</v>
       </c>
       <c r="B9" t="n">
         <v>92869</v>
@@ -1511,7 +1504,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1527,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655276</v>
+        <v>655280</v>
       </c>
       <c r="R9" t="n">
-        <v>6675638</v>
+        <v>6675629</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1562,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,37 +1592,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112071516</v>
+        <v>119002682</v>
       </c>
       <c r="B10" t="n">
-        <v>91435</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1645,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655233</v>
+        <v>655276</v>
       </c>
       <c r="R10" t="n">
-        <v>6675613</v>
+        <v>6675638</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1675,36 +1668,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rätt fuktig mark med gran och tall. Ca 10x15 cm bred och drygt 15 cm hög ovan mark. Klen, torr, vitaktig fot. Ljusgula, långa grenar med klargula toppar. Doftar svagt, lite smörigt. Kan ej beskriva smaken. Efter ett dygn i plastpåse doftar den svagt av läder/saffran om grenarna, samma doft som vedticka men mycket svagare.</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1723,37 +1710,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119002672</v>
+        <v>112071516</v>
       </c>
       <c r="B11" t="n">
-        <v>91443</v>
+        <v>91435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5754</v>
+        <v>5747</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1769,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655294</v>
+        <v>655233</v>
       </c>
       <c r="R11" t="n">
-        <v>6675660</v>
+        <v>6675613</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1799,30 +1786,36 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rätt fuktig mark med gran och tall. Ca 10x15 cm bred och drygt 15 cm hög ovan mark. Klen, torr, vitaktig fot. Ljusgula, långa grenar med klargula toppar. Doftar svagt, lite smörigt. Kan ej beskriva smaken. Efter ett dygn i plastpåse doftar den svagt av läder/saffran om grenarna, samma doft som vedticka men mycket svagare.</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1841,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111685514</v>
+        <v>119002672</v>
       </c>
       <c r="B12" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,37 +1845,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mumsarby , Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655384</v>
+        <v>655294</v>
       </c>
       <c r="R12" t="n">
-        <v>6675716</v>
+        <v>6675660</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1909,27 +1910,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lång rad med fruktkroppar nära ett kärr där en del gran finns, annars mest tall runtomkring.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,7 +1934,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1957,46 +1952,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111685525</v>
+        <v>111685514</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2004,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655287</v>
+        <v>655384</v>
       </c>
       <c r="R13" t="n">
-        <v>6675700</v>
+        <v>6675716</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2039,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,7 +2035,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lång rad med fruktkroppar nära ett kärr där en del gran finns, annars mest tall runtomkring.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,6 +2049,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2076,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111474623</v>
+        <v>135229457</v>
       </c>
       <c r="B14" t="n">
-        <v>101326</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,38 +2079,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mumsarby 1089 m NW, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655407</v>
+        <v>655383</v>
       </c>
       <c r="R14" t="n">
-        <v>6675770</v>
+        <v>6675673</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2145,22 +2145,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,56 +2183,68 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111514338</v>
+        <v>135229455</v>
       </c>
       <c r="B15" t="n">
-        <v>101326</v>
+        <v>57860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mumsarby 1046 m NW, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655238</v>
+        <v>655273</v>
       </c>
       <c r="R15" t="n">
-        <v>6675614</v>
+        <v>6675639</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2256,22 +2268,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Uppgrävt getingbo.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,64 +2311,68 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111514339</v>
+        <v>135229456</v>
       </c>
       <c r="B16" t="n">
-        <v>101326</v>
+        <v>57860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mumsarby 1093 m NW, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655411</v>
+        <v>655295</v>
       </c>
       <c r="R16" t="n">
-        <v>6675762</v>
+        <v>6675672</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2375,22 +2396,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Uppgrävt getingbo.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,14 +2439,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111514343</v>
+        <v>135229443</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>57162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2428,41 +2458,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mumsarby 1107 m NW, Upl</t>
+          <t>Högmon, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655378</v>
+        <v>655353</v>
       </c>
       <c r="R17" t="n">
-        <v>6675763</v>
+        <v>6675591</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,22 +2528,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,14 +2566,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119002698</v>
+        <v>135229446</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>57162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,27 +2585,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2567,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655287</v>
+        <v>655278</v>
       </c>
       <c r="R18" t="n">
-        <v>6675660</v>
+        <v>6675687</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2597,22 +2651,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,14 +2689,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119002700</v>
+        <v>135229447</v>
       </c>
       <c r="B19" t="n">
-        <v>101326</v>
+        <v>57162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2650,38 +2708,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Valtins, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655395</v>
+        <v>655265</v>
       </c>
       <c r="R19" t="n">
-        <v>6675760</v>
+        <v>6675723</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2708,22 +2774,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2746,36 +2812,40 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112071519</v>
+        <v>135229448</v>
       </c>
       <c r="B20" t="n">
-        <v>91428</v>
+        <v>57162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>256756</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2783,12 +2853,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2796,10 +2867,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655241</v>
+        <v>655259</v>
       </c>
       <c r="R20" t="n">
-        <v>6675610</v>
+        <v>6675719</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2826,27 +2897,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fuktig mark med gran och tall. Ca 15 cm hög. Vitaktiga/cremefärgade grenar. Liten bit insamlad.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,7 +2935,2705 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135229449</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>655287</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6675756</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135229450</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>655227</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6675934</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135229451</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>655241</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6675917</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135229452</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>655256</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6675930</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135229453</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>655284</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6675876</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135229470</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>655188</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6675746</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135229461</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>655263</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6675708</v>
+      </c>
+      <c r="S27" t="n">
+        <v>58</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135229438</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>655313</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6675747</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135229439</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>655222</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6675806</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135229440</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56896</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>655304</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6675768</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135229478</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>655379</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6675703</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>111685525</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mumsarby , Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>655287</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6675700</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135229484</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>655320</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6675680</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135229488</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>655229</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6675697</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135229490</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>655298</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6675764</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135229495</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>655288</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6675824</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>111474623</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mumsarby 1089 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>655407</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6675770</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111514338</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mumsarby 1046 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>655238</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6675614</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111514339</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mumsarby 1093 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>655411</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6675762</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111514343</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mumsarby 1107 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>655378</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6675763</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>119002698</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>655287</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6675660</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>119002700</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Valtins, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>655395</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6675760</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112071519</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>655241</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6675610</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fuktig mark med gran och tall. Ca 15 cm hög. Vitaktiga/cremefärgade grenar. Liten bit insamlad.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111514314</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112071514</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002667</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002668</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107121708</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229477</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1589,6 +1629,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002680</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1707,6 +1752,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002682</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1831,6 +1881,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112071516</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1949,6 +2004,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002672</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2065,6 +2125,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111685514</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2188,6 +2253,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229457</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2316,6 +2386,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229455</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2444,6 +2519,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229456</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2571,6 +2651,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229443</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2694,6 +2779,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229446</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2817,6 +2907,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229447</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2940,6 +3035,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229448</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3067,6 +3167,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229449</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3190,6 +3295,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229450</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3313,6 +3423,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229451</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3436,6 +3551,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229452</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3559,6 +3679,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229453</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3686,6 +3811,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229470</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3809,6 +3939,11 @@
           <t>EKOLISTAN</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229461</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3928,6 +4063,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229438</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4047,6 +4187,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229439</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4163,6 +4308,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229440</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4274,6 +4424,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229478</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4393,6 +4548,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111685525</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4504,6 +4664,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229484</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4615,6 +4780,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229488</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4726,6 +4896,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229490</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4837,6 +5012,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229495</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4948,6 +5128,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474623</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5059,6 +5244,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111514338</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5178,6 +5368,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111514339</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5289,6 +5484,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111514343</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5400,6 +5600,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002698</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5511,6 +5716,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002700</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5634,8 +5844,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112071519</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>135229477</v>
       </c>
       <c r="B8" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>135229457</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135229455</v>
       </c>
       <c r="B15" t="n">
-        <v>57860</v>
+        <v>57865</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135229456</v>
       </c>
       <c r="B16" t="n">
-        <v>57860</v>
+        <v>57865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>135229443</v>
       </c>
       <c r="B17" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>135229446</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135229447</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135229448</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>135229449</v>
       </c>
       <c r="B21" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>135229450</v>
       </c>
       <c r="B22" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>135229451</v>
       </c>
       <c r="B23" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>135229452</v>
       </c>
       <c r="B24" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>135229453</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>135229470</v>
       </c>
       <c r="B26" t="n">
-        <v>58519</v>
+        <v>58524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>135229461</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>135229438</v>
       </c>
       <c r="B28" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>135229439</v>
       </c>
       <c r="B29" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>135229440</v>
       </c>
       <c r="B30" t="n">
-        <v>56896</v>
+        <v>56901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>135229478</v>
       </c>
       <c r="B31" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>135229484</v>
       </c>
       <c r="B33" t="n">
-        <v>106358</v>
+        <v>106413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135229488</v>
       </c>
       <c r="B34" t="n">
-        <v>106358</v>
+        <v>106413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106358</v>
+        <v>106413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>135229495</v>
       </c>
       <c r="B36" t="n">
-        <v>106358</v>
+        <v>106413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>135229477</v>
       </c>
       <c r="B8" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>135229478</v>
       </c>
       <c r="B31" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>135229484</v>
       </c>
       <c r="B33" t="n">
-        <v>106413</v>
+        <v>106440</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135229488</v>
       </c>
       <c r="B34" t="n">
-        <v>106413</v>
+        <v>106440</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106413</v>
+        <v>106440</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>135229495</v>
       </c>
       <c r="B36" t="n">
-        <v>106413</v>
+        <v>106440</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119002680</v>
+        <v>135229477</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>96486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,34 +1409,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1444,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655280</v>
+        <v>655340</v>
       </c>
       <c r="R8" t="n">
-        <v>6675629</v>
+        <v>6675648</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1474,22 +1467,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,13 +1508,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119002680</t>
+          <t>https://artportalen.se/Sighting/135229477</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119002682</v>
+        <v>119002680</v>
       </c>
       <c r="B9" t="n">
         <v>92869</v>
@@ -1551,7 +1544,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1567,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655276</v>
+        <v>655280</v>
       </c>
       <c r="R9" t="n">
-        <v>6675638</v>
+        <v>6675629</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1602,7 +1595,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1605,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,43 +1631,43 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119002682</t>
+          <t>https://artportalen.se/Sighting/119002680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112071516</v>
+        <v>119002682</v>
       </c>
       <c r="B10" t="n">
-        <v>91435</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1690,10 +1683,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655233</v>
+        <v>655276</v>
       </c>
       <c r="R10" t="n">
-        <v>6675613</v>
+        <v>6675638</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1720,36 +1713,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rätt fuktig mark med gran och tall. Ca 10x15 cm bred och drygt 15 cm hög ovan mark. Klen, torr, vitaktig fot. Ljusgula, långa grenar med klargula toppar. Doftar svagt, lite smörigt. Kan ej beskriva smaken. Efter ett dygn i plastpåse doftar den svagt av läder/saffran om grenarna, samma doft som vedticka men mycket svagare.</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1767,43 +1754,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112071516</t>
+          <t>https://artportalen.se/Sighting/119002682</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119002672</v>
+        <v>112071516</v>
       </c>
       <c r="B11" t="n">
-        <v>91443</v>
+        <v>91435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5754</v>
+        <v>5747</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1819,10 +1806,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655294</v>
+        <v>655233</v>
       </c>
       <c r="R11" t="n">
-        <v>6675660</v>
+        <v>6675613</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1849,30 +1836,36 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rätt fuktig mark med gran och tall. Ca 10x15 cm bred och drygt 15 cm hög ovan mark. Klen, torr, vitaktig fot. Ljusgula, långa grenar med klargula toppar. Doftar svagt, lite smörigt. Kan ej beskriva smaken. Efter ett dygn i plastpåse doftar den svagt av läder/saffran om grenarna, samma doft som vedticka men mycket svagare.</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1890,16 +1883,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119002672</t>
+          <t>https://artportalen.se/Sighting/112071516</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111685514</v>
+        <v>119002672</v>
       </c>
       <c r="B12" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,37 +1900,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mumsarby , Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655384</v>
+        <v>655294</v>
       </c>
       <c r="R12" t="n">
-        <v>6675716</v>
+        <v>6675660</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1964,27 +1965,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lång rad med fruktkroppar nära ett kärr där en del gran finns, annars mest tall runtomkring.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1993,7 +1989,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2011,52 +2006,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111685514</t>
+          <t>https://artportalen.se/Sighting/119002672</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111685525</v>
+        <v>111685514</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2064,10 +2050,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655287</v>
+        <v>655384</v>
       </c>
       <c r="R13" t="n">
-        <v>6675700</v>
+        <v>6675716</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2099,7 +2085,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2109,7 +2095,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lång rad med fruktkroppar nära ett kärr där en del gran finns, annars mest tall runtomkring.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,6 +2109,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2135,16 +2127,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111685525</t>
+          <t>https://artportalen.se/Sighting/111685514</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111474623</v>
+        <v>135229457</v>
       </c>
       <c r="B14" t="n">
-        <v>101326</v>
+        <v>57977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,38 +2144,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mumsarby 1089 m NW, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655407</v>
+        <v>655383</v>
       </c>
       <c r="R14" t="n">
-        <v>6675770</v>
+        <v>6675673</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2210,22 +2210,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,61 +2248,73 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111474623</t>
+          <t>https://artportalen.se/Sighting/135229457</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111514338</v>
+        <v>135229455</v>
       </c>
       <c r="B15" t="n">
-        <v>101326</v>
+        <v>57865</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mumsarby 1046 m NW, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655238</v>
+        <v>655273</v>
       </c>
       <c r="R15" t="n">
-        <v>6675614</v>
+        <v>6675639</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2326,22 +2338,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Uppgrävt getingbo.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,69 +2381,73 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111514338</t>
+          <t>https://artportalen.se/Sighting/135229455</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111514339</v>
+        <v>135229456</v>
       </c>
       <c r="B16" t="n">
-        <v>101326</v>
+        <v>57865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mumsarby 1093 m NW, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655411</v>
+        <v>655295</v>
       </c>
       <c r="R16" t="n">
-        <v>6675762</v>
+        <v>6675672</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2450,22 +2471,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Uppgrävt getingbo.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2488,19 +2514,23 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111514339</t>
+          <t>https://artportalen.se/Sighting/135229456</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111514343</v>
+        <v>135229443</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,41 +2538,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mumsarby 1107 m NW, Upl</t>
+          <t>Högmon, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655378</v>
+        <v>655353</v>
       </c>
       <c r="R17" t="n">
-        <v>6675763</v>
+        <v>6675591</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2566,22 +2608,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,19 +2646,23 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111514343</t>
+          <t>https://artportalen.se/Sighting/135229443</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119002698</v>
+        <v>135229446</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,27 +2670,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2652,10 +2706,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655287</v>
+        <v>655278</v>
       </c>
       <c r="R18" t="n">
-        <v>6675660</v>
+        <v>6675687</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2682,22 +2736,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2720,19 +2774,23 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119002698</t>
+          <t>https://artportalen.se/Sighting/135229446</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119002700</v>
+        <v>135229447</v>
       </c>
       <c r="B19" t="n">
-        <v>101326</v>
+        <v>57167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2740,38 +2798,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Valtins, Upl</t>
+          <t>Persbomossen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655395</v>
+        <v>655265</v>
       </c>
       <c r="R19" t="n">
-        <v>6675760</v>
+        <v>6675723</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2798,22 +2864,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,41 +2902,45 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119002700</t>
+          <t>https://artportalen.se/Sighting/135229447</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112071519</v>
+        <v>135229448</v>
       </c>
       <c r="B20" t="n">
-        <v>91428</v>
+        <v>57167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>256756</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2878,12 +2948,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2891,10 +2962,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655241</v>
+        <v>655259</v>
       </c>
       <c r="R20" t="n">
-        <v>6675610</v>
+        <v>6675719</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2921,27 +2992,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fuktig mark med gran och tall. Ca 15 cm hög. Vitaktiga/cremefärgade grenar. Liten bit insamlad.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2964,8 +3030,2821 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229448</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135229449</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>655287</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6675756</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229449</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135229450</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>655227</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6675934</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229450</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135229451</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>655241</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6675917</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229451</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135229452</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>655256</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6675930</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229452</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135229453</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>655284</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6675876</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229453</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135229470</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58524</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>655188</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6675746</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229470</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135229461</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>655263</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6675708</v>
+      </c>
+      <c r="S27" t="n">
+        <v>58</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229461</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135229438</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>655313</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6675747</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229438</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135229439</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>655222</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6675806</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229439</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135229440</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56901</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>655304</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6675768</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229440</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135229478</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98295</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>655379</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6675703</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229478</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>111685525</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mumsarby , Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>655287</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6675700</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111685525</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135229484</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106445</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>655320</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6675680</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229484</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135229488</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106445</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>655229</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6675697</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229488</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135229490</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106445</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>655298</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6675764</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229490</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135229495</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106445</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>655288</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6675824</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229495</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>111474623</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mumsarby 1089 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>655407</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6675770</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474623</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111514338</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mumsarby 1046 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>655238</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6675614</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111514338</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111514339</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mumsarby 1093 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>655411</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6675762</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111514339</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111514343</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mumsarby 1107 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>655378</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6675763</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111514343</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>119002698</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>655287</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6675660</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002698</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>119002700</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Valtins, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>655395</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6675760</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119002700</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112071519</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Persbomossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>655241</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6675610</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fuktig mark med gran och tall. Ca 15 cm hög. Vitaktiga/cremefärgade grenar. Liten bit insamlad.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112071519</t>
         </is>
@@ -2992,6 +5871,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>135229477</v>
       </c>
       <c r="B8" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>135229478</v>
       </c>
       <c r="B31" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>135229484</v>
       </c>
       <c r="B33" t="n">
-        <v>106445</v>
+        <v>106447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135229488</v>
       </c>
       <c r="B34" t="n">
-        <v>106445</v>
+        <v>106447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106445</v>
+        <v>106447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>135229495</v>
       </c>
       <c r="B36" t="n">
-        <v>106445</v>
+        <v>106447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
